--- a/AAII_Financials/Yearly/MTEK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MTEK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
   <si>
     <t>MTEK</t>
   </si>
@@ -1152,8 +1152,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>200</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1195,7 +1195,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-5100</v>
+        <v>-5300</v>
       </c>
       <c r="E21" s="3">
         <v>-1200</v>
@@ -1236,8 +1236,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>200</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>3</v>
@@ -1656,8 +1656,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="E43" s="3">
-        <v>3800</v>
+        <v>3500</v>
       </c>
       <c r="F43" s="3">
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="G43" s="3">
         <v>2000</v>
@@ -2075,14 +2075,14 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
+        <v>200</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
@@ -2574,7 +2574,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="E58" s="3">
         <v>700</v>
@@ -2616,7 +2616,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
